--- a/ValueSet-mii-vs-mikrobio-organismen-snomedct.xlsx
+++ b/ValueSet-mii-vs-mikrobio-organismen-snomedct.xlsx
@@ -13,12 +13,15 @@
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
     <sheet name="Include #4" r:id="rId8" sheetId="6"/>
     <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -138,6 +141,15 @@
   </si>
   <si>
     <t>49872002</t>
+  </si>
+  <si>
+    <t>441649000</t>
+  </si>
+  <si>
+    <t>76222001</t>
+  </si>
+  <si>
+    <t>106763003</t>
   </si>
 </sst>
 </file>
@@ -399,7 +411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -427,7 +439,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -479,7 +491,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -531,7 +543,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -583,7 +595,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -607,7 +619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -635,7 +647,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -659,7 +671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -687,6 +699,58 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
         <v>39</v>
       </c>
     </row>
@@ -709,4 +773,108 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>